--- a/sheets/민요/검수/는실 타령-2.xlsx
+++ b/sheets/민요/검수/는실 타령-2.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/는실 타령-2.xlsx
+++ b/sheets/민요/검수/는실 타령-2.xlsx
@@ -1734,6 +1734,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1746,10 +1749,10 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="77.61" customHeight="1">
+    <row r="2" ht="40.82" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1764,7 +1767,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="77.61" customHeight="1">
+    <row r="3" ht="90.88" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1819,7 +1822,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="77.61" customHeight="1">
+    <row r="4" ht="90.88" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -1866,7 +1869,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="77.61" customHeight="1">
+    <row r="5" ht="90.88" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -1917,7 +1920,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="77.61" customHeight="1">
+    <row r="6" ht="90.88" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -1969,7 +1972,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="77.61" customHeight="1">
+    <row r="7" ht="90.88" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
@@ -2012,7 +2015,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="77.61" customHeight="1">
+    <row r="8" ht="90.88" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="23"/>
       <c r="C8" s="25"/>
@@ -2055,7 +2058,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="77.61" customHeight="1">
+    <row r="9" ht="90.88" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23"/>
       <c r="C9" s="25"/>
@@ -2097,7 +2100,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="77.61" customHeight="1">
+    <row r="10" ht="90.88" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23"/>
       <c r="C10" s="27"/>
@@ -2146,6 +2149,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="98"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/는실 타령-2.xlsx
+++ b/sheets/민요/검수/는실 타령-2.xlsx
@@ -1739,13 +1739,13 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
